--- a/demo-excel/11-HRMS-Enterprise-demo.xlsx
+++ b/demo-excel/11-HRMS-Enterprise-demo.xlsx
@@ -1183,7 +1183,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>• Kustomisasi: ganti nama tunjangan, tarif, daftar departemen/status, band gaji, bobot KPI, tabel rating, dan 2 kolom kustom di PARAMETER tanpa mengubah rumus. Perlu modul khusus? Hubungi WhatsApp 089623291732 (layanan Custom Pro).</t>
+          <t>• Kustomisasi: ganti nama tunjangan, tarif, daftar departemen/status, band gaji, bobot KPI, tabel rating, dan 2 kolom kustom di PARAMETER tanpa mengubah rumus..</t>
         </is>
       </c>
     </row>
